--- a/artfynd/S 7016-2022 artfynd.xlsx
+++ b/artfynd/S 7016-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065205</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065206</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065207</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065224</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065225</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065226</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280972</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103113285</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468689</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,6 +2287,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065223</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2468,6 +2548,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280975</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2577,6 +2662,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123758066</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2689,6 +2779,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122159424</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2801,6 +2896,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122159464</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209569</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3023,6 +3128,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209570</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3134,6 +3244,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209571</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3240,6 +3355,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210344</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210345</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3457,6 +3582,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2696943</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3563,6 +3693,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3390875</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3664,6 +3799,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065198</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3765,6 +3905,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065199</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3866,6 +4011,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065200</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3972,6 +4122,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4959479</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4092,6 +4247,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5303597</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4202,6 +4362,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103108289</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4312,6 +4477,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103108421</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4422,6 +4592,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103108438</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4532,6 +4707,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103108611</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4642,6 +4822,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103108622</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4753,6 +4938,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5789560</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4864,6 +5054,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5789561</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4965,6 +5160,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065210</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5071,6 +5271,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065211</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5177,6 +5382,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065213</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5283,6 +5493,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065216</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5384,6 +5599,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065217</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5494,6 +5714,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109085</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5604,6 +5829,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109086</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5714,6 +5944,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109088</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5824,6 +6059,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109090</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5934,6 +6174,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109091</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6044,6 +6289,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109095</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6154,6 +6404,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109097</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6264,6 +6519,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109099</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6374,6 +6634,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109100</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6484,6 +6749,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109101</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6594,6 +6864,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109102</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6704,6 +6979,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109104</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6814,6 +7094,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109105</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6924,6 +7209,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109106</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7034,6 +7324,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109107</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7144,6 +7439,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109108</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7254,6 +7554,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109109</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7364,6 +7669,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109110</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7474,6 +7784,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109111</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7584,6 +7899,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109112</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7694,6 +8014,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109114</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7804,6 +8129,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109116</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7914,6 +8244,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109117</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8024,6 +8359,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109119</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8134,6 +8474,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109120</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8244,6 +8589,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109121</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8354,6 +8704,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109122</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8464,6 +8819,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109126</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8574,6 +8934,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109127</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8684,6 +9049,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109129</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8794,6 +9164,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109132</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8904,6 +9279,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109134</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9014,6 +9394,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109135</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9124,6 +9509,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109137</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9234,6 +9624,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109139</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9344,6 +9739,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109142</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9454,6 +9854,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109143</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9564,6 +9969,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109144</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9674,6 +10084,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109148</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9784,6 +10199,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109150</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9894,6 +10314,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109152</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10004,6 +10429,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109153</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10114,6 +10544,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109154</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10224,6 +10659,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103109156</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10349,6 +10789,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468681</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10475,8 +10920,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280976</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>